--- a/docs/Architecture Decisions.xlsx
+++ b/docs/Architecture Decisions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Data Engineering PREP\Portfolio and Profiles Improvement\FlagShip Project - retail_supply_chain_lakehouse\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{545F658F-402A-456E-A56D-C35DBB466497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D85051-4548-4844-A4CC-DDB9BA55E9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{09F4E8B7-495A-4BF3-94FA-31BF73904402}"/>
   </bookViews>
@@ -117,7 +117,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,7 +126,20 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -173,12 +186,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -518,96 +534,96 @@
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultColWidth="32.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>23</v>
       </c>
     </row>
